--- a/docs/phase1/EGLE360_PLAN_Funktionsmatrix.xlsx
+++ b/docs/phase1/EGLE360_PLAN_Funktionsmatrix.xlsx
@@ -595,7 +595,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>Offen</t>
+          <t>Umgesetzt (Phase 4, Teil 1)</t>
         </is>
       </c>
     </row>
@@ -666,7 +666,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>Offen</t>
+          <t>Teilweise (Phase 4, Teil 1): leeres Dokument mit wählbarem Format; Erstellung aus Office/CAD offen</t>
         </is>
       </c>
     </row>
@@ -741,7 +741,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>Offen</t>
+          <t>Umgesetzt (Phase 4, Teil 1)</t>
         </is>
       </c>
     </row>
@@ -883,7 +883,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>Offen</t>
+          <t>Teilweise (Phase 4, Teil 1): Seiten aus einer anderen PDF einfügen; Mehrfachauswahl von Dateien offen</t>
         </is>
       </c>
     </row>
@@ -950,7 +950,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>Offen</t>
+          <t>Teilweise (Phase 4, Teil 1): Seitenbereich in neue Datei extrahieren; Aufteilen nach Lesezeichen oder Seitenzahl offen</t>
         </is>
       </c>
     </row>
@@ -1021,7 +1021,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>Offen</t>
+          <t>Umgesetzt (Phase 4, Teil 1)</t>
         </is>
       </c>
     </row>
@@ -1092,7 +1092,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>Offen</t>
+          <t>Umgesetzt (Phase 4, Teil 1)</t>
         </is>
       </c>
     </row>
@@ -1234,7 +1234,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>Offen</t>
+          <t>Umgesetzt (Phase 4, Teil 1)</t>
         </is>
       </c>
     </row>
@@ -1305,7 +1305,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>Offen</t>
+          <t>Teilweise (Phase 4, Teil 1): Seite vor/zurück per Befehl; Drag &amp; Drop in Miniaturen offen</t>
         </is>
       </c>
     </row>
@@ -1376,7 +1376,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>Offen</t>
+          <t>Umgesetzt (Phase 4, Teil 1)</t>
         </is>
       </c>
     </row>
@@ -1447,7 +1447,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>Offen</t>
+          <t>Umgesetzt (Phase 4, Teil 1)</t>
         </is>
       </c>
     </row>
@@ -1727,7 +1727,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>Offen</t>
+          <t>Teilweise (Phase 4, Teil 1): Seitenlabels werden angezeigt; Bearbeiten offen</t>
         </is>
       </c>
     </row>
@@ -1798,7 +1798,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>Offen</t>
+          <t>Teilweise (Phase 4, Teil 1): Lesezeichen anzeigen und anspringen; Bearbeiten offen</t>
         </is>
       </c>
     </row>
@@ -2082,7 +2082,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>Offen</t>
+          <t>Teilweise (Phase 4, Teil 1): Eigenschaften und Metadaten anzeigen; Bearbeiten offen</t>
         </is>
       </c>
     </row>
@@ -3194,7 +3194,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>Offen</t>
+          <t>Umgesetzt (Phase 4, Teil 1)</t>
         </is>
       </c>
     </row>
@@ -3478,7 +3478,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>Offen</t>
+          <t>Umgesetzt (Phase 4, Teil 1)</t>
         </is>
       </c>
     </row>
@@ -3549,7 +3549,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>Offen</t>
+          <t>Umgesetzt (Phase 4, Teil 1)</t>
         </is>
       </c>
     </row>
@@ -3971,7 +3971,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>Offen</t>
+          <t>Teilweise (Phase 4, Teil 1): Seitenleiste mit Miniaturen und Lesezeichen</t>
         </is>
       </c>
     </row>
@@ -4464,7 +4464,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>Offen</t>
+          <t>Teilweise (Phase 4, Teil 1): Statusleiste mit Pfad, Seitenformat und Zoom</t>
         </is>
       </c>
     </row>

--- a/docs/phase1/EGLE360_PLAN_Funktionsmatrix.xlsx
+++ b/docs/phase1/EGLE360_PLAN_Funktionsmatrix.xlsx
@@ -3971,7 +3971,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>Teilweise (Phase 4, Teil 1): Seitenleiste mit Miniaturen und Lesezeichen</t>
+          <t>Teilweise (Phase 4, Teil 2): Seitenleiste mit Miniaturen, Lesezeichen und Suche; Markierungsliste unten</t>
         </is>
       </c>
     </row>
@@ -4188,7 +4188,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>Offen</t>
+          <t>Umgesetzt (Phase 4, Teil 2): Suche über alle Seiten, Trefferliste, Hervorhebung, F3</t>
         </is>
       </c>
     </row>
@@ -4535,7 +4535,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>Offen</t>
+          <t>Teilweise (Phase 4, Teil 2): Kontextmenüs für Miniaturen und Markierungen</t>
         </is>
       </c>
     </row>
@@ -7327,7 +7327,7 @@
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>Offen</t>
+          <t>Umgesetzt (Phase 4, Teil 2)</t>
         </is>
       </c>
     </row>
@@ -7398,7 +7398,7 @@
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
-          <t>Offen</t>
+          <t>Umgesetzt (Phase 4, Teil 2)</t>
         </is>
       </c>
     </row>
@@ -7469,7 +7469,7 @@
       </c>
       <c r="O100" s="2" t="inlineStr">
         <is>
-          <t>Offen</t>
+          <t>Umgesetzt (Phase 4, Teil 2)</t>
         </is>
       </c>
     </row>
@@ -7607,7 +7607,7 @@
       <c r="N102" s="2" t="inlineStr"/>
       <c r="O102" s="2" t="inlineStr">
         <is>
-          <t>Offen</t>
+          <t>Umgesetzt (Phase 4, Teil 2)</t>
         </is>
       </c>
     </row>
@@ -7674,7 +7674,7 @@
       <c r="N103" s="2" t="inlineStr"/>
       <c r="O103" s="2" t="inlineStr">
         <is>
-          <t>Offen</t>
+          <t>Umgesetzt (Phase 4, Teil 2)</t>
         </is>
       </c>
     </row>
@@ -7741,7 +7741,7 @@
       <c r="N104" s="2" t="inlineStr"/>
       <c r="O104" s="2" t="inlineStr">
         <is>
-          <t>Offen</t>
+          <t>Umgesetzt (Phase 4, Teil 2)</t>
         </is>
       </c>
     </row>
@@ -7812,7 +7812,7 @@
       </c>
       <c r="O105" s="2" t="inlineStr">
         <is>
-          <t>Offen</t>
+          <t>Umgesetzt (Phase 4, Teil 2)</t>
         </is>
       </c>
     </row>
@@ -8021,7 +8021,7 @@
       </c>
       <c r="O108" s="2" t="inlineStr">
         <is>
-          <t>Offen</t>
+          <t>Umgesetzt (Phase 4, Teil 2)</t>
         </is>
       </c>
     </row>
@@ -8159,7 +8159,7 @@
       </c>
       <c r="O110" s="2" t="inlineStr">
         <is>
-          <t>Offen</t>
+          <t>Umgesetzt (Phase 4, Teil 2)</t>
         </is>
       </c>
     </row>
@@ -8360,7 +8360,7 @@
       <c r="N113" s="2" t="inlineStr"/>
       <c r="O113" s="2" t="inlineStr">
         <is>
-          <t>Offen</t>
+          <t>Umgesetzt (Phase 4, Teil 2)</t>
         </is>
       </c>
     </row>
@@ -8494,7 +8494,7 @@
       <c r="N115" s="2" t="inlineStr"/>
       <c r="O115" s="2" t="inlineStr">
         <is>
-          <t>Offen</t>
+          <t>Teilweise (Phase 4, Teil 2): Bereich hervorheben; an Textauswahl gebunden offen</t>
         </is>
       </c>
     </row>
@@ -9976,7 +9976,7 @@
       <c r="N137" s="2" t="inlineStr"/>
       <c r="O137" s="2" t="inlineStr">
         <is>
-          <t>Offen</t>
+          <t>Umgesetzt (Phase 4, Teil 2): Klick, Strg+Klick, Strg+A</t>
         </is>
       </c>
     </row>
@@ -10039,7 +10039,7 @@
       <c r="N138" s="2" t="inlineStr"/>
       <c r="O138" s="2" t="inlineStr">
         <is>
-          <t>Offen</t>
+          <t>Teilweise (Phase 4, Teil 2): Verschieben und Skalieren; Drehen offen</t>
         </is>
       </c>
     </row>
@@ -10177,7 +10177,7 @@
       </c>
       <c r="O140" s="2" t="inlineStr">
         <is>
-          <t>Offen</t>
+          <t>Teilweise (Phase 4, Teil 2): Kopieren und Einfügen (Strg+C, Strg+V); Ausschneiden und an Position einfügen offen</t>
         </is>
       </c>
     </row>
@@ -10244,7 +10244,7 @@
       </c>
       <c r="O141" s="2" t="inlineStr">
         <is>
-          <t>Offen</t>
+          <t>Umgesetzt (Phase 4, Teil 2): Strg+D</t>
         </is>
       </c>
     </row>
@@ -10508,7 +10508,7 @@
       <c r="N145" s="2" t="inlineStr"/>
       <c r="O145" s="2" t="inlineStr">
         <is>
-          <t>Offen</t>
+          <t>Teilweise (Phase 4, Teil 2): Vordergrund und Hintergrund über Kontextmenü</t>
         </is>
       </c>
     </row>
@@ -10646,7 +10646,7 @@
       </c>
       <c r="O147" s="2" t="inlineStr">
         <is>
-          <t>Offen</t>
+          <t>Teilweise (Phase 4, Teil 2): Farbe, Linienbreite, Deckkraft, Füllung, Text, Kommentar</t>
         </is>
       </c>
     </row>
@@ -10784,7 +10784,7 @@
       </c>
       <c r="O149" s="2" t="inlineStr">
         <is>
-          <t>Offen</t>
+          <t>Umgesetzt (Phase 4, Teil 2)</t>
         </is>
       </c>
     </row>
@@ -11060,7 +11060,7 @@
       <c r="N153" s="2" t="inlineStr"/>
       <c r="O153" s="2" t="inlineStr">
         <is>
-          <t>Offen</t>
+          <t>Umgesetzt (Phase 4, Teil 2): Umschalttaste beim Zeichnen</t>
         </is>
       </c>
     </row>
@@ -11738,7 +11738,7 @@
       <c r="N163" s="2" t="inlineStr"/>
       <c r="O163" s="2" t="inlineStr">
         <is>
-          <t>Offen</t>
+          <t>Umgesetzt (Phase 4, Teil 2): Eckpunkte von Linien, Polygonen und Messungen ziehen</t>
         </is>
       </c>
     </row>
@@ -11809,7 +11809,7 @@
       </c>
       <c r="O164" s="2" t="inlineStr">
         <is>
-          <t>Offen</t>
+          <t>Teilweise (Phase 5, Teil 1): Liste aller Markierungen des Dokuments</t>
         </is>
       </c>
     </row>
@@ -11876,7 +11876,7 @@
       </c>
       <c r="O165" s="2" t="inlineStr">
         <is>
-          <t>Offen</t>
+          <t>Teilweise (Phase 5, Teil 1): Seite, Art, Wert, Text, Maßstab, Autor, Datum</t>
         </is>
       </c>
     </row>
@@ -11943,7 +11943,7 @@
       </c>
       <c r="O166" s="2" t="inlineStr">
         <is>
-          <t>Offen</t>
+          <t>Teilweise (Phase 5, Teil 1): Sortieren und Filtern; Gruppieren offen</t>
         </is>
       </c>
     </row>
@@ -12278,7 +12278,7 @@
       </c>
       <c r="O171" s="2" t="inlineStr">
         <is>
-          <t>Offen</t>
+          <t>Teilweise (Phase 5, Teil 1): Summen je Messart in der Liste</t>
         </is>
       </c>
     </row>
@@ -12345,7 +12345,7 @@
       </c>
       <c r="O172" s="2" t="inlineStr">
         <is>
-          <t>Offen</t>
+          <t>Teilweise (Phase 5, Teil 1): CSV-Export für Excel; XLSX offen</t>
         </is>
       </c>
     </row>
@@ -12885,7 +12885,7 @@
       </c>
       <c r="O180" s="2" t="inlineStr">
         <is>
-          <t>Offen</t>
+          <t>Umgesetzt (Phase 5, Teil 1)</t>
         </is>
       </c>
     </row>
@@ -12960,7 +12960,7 @@
       </c>
       <c r="O181" s="2" t="inlineStr">
         <is>
-          <t>Offen</t>
+          <t>Umgesetzt (Phase 5, Teil 1)</t>
         </is>
       </c>
     </row>
@@ -13031,7 +13031,7 @@
       <c r="N182" s="2" t="inlineStr"/>
       <c r="O182" s="2" t="inlineStr">
         <is>
-          <t>Offen</t>
+          <t>Umgesetzt (Phase 5, Teil 1)</t>
         </is>
       </c>
     </row>
@@ -13106,7 +13106,7 @@
       </c>
       <c r="O183" s="2" t="inlineStr">
         <is>
-          <t>Offen</t>
+          <t>Umgesetzt (Phase 5, Teil 1): Fläche mit Umfang</t>
         </is>
       </c>
     </row>
@@ -13587,7 +13587,7 @@
       <c r="N190" s="2" t="inlineStr"/>
       <c r="O190" s="2" t="inlineStr">
         <is>
-          <t>Offen</t>
+          <t>Umgesetzt (Phase 5, Teil 1)</t>
         </is>
       </c>
     </row>
@@ -13926,7 +13926,7 @@
       <c r="N195" s="2" t="inlineStr"/>
       <c r="O195" s="2" t="inlineStr">
         <is>
-          <t>Offen</t>
+          <t>Umgesetzt (Phase 5, Teil 1)</t>
         </is>
       </c>
     </row>
@@ -14052,7 +14052,7 @@
       <c r="N197" s="2" t="inlineStr"/>
       <c r="O197" s="2" t="inlineStr">
         <is>
-          <t>Offen</t>
+          <t>Teilweise (Phase 5, Teil 1): Summen in der Liste und für ausgewählte Messungen</t>
         </is>
       </c>
     </row>
@@ -14328,7 +14328,7 @@
       </c>
       <c r="O201" s="2" t="inlineStr">
         <is>
-          <t>Offen</t>
+          <t>Umgesetzt (Phase 5, Teil 1): übliche Maßstäbe 1:1 bis 1:2000 je Seite</t>
         </is>
       </c>
     </row>
@@ -14395,7 +14395,7 @@
       </c>
       <c r="O202" s="2" t="inlineStr">
         <is>
-          <t>Offen</t>
+          <t>Umgesetzt (Phase 5, Teil 1)</t>
         </is>
       </c>
     </row>
@@ -14592,7 +14592,7 @@
       </c>
       <c r="O205" s="2" t="inlineStr">
         <is>
-          <t>Offen</t>
+          <t>Teilweise (Phase 5, Teil 1): m, cm, mm</t>
         </is>
       </c>
     </row>
@@ -14726,7 +14726,7 @@
       <c r="N207" s="2" t="inlineStr"/>
       <c r="O207" s="2" t="inlineStr">
         <is>
-          <t>Offen</t>
+          <t>Teilweise (Phase 5, Teil 1): Mengenliste mit Summen und CSV-Export</t>
         </is>
       </c>
     </row>

--- a/docs/phase1/EGLE360_PLAN_Funktionsmatrix.xlsx
+++ b/docs/phase1/EGLE360_PLAN_Funktionsmatrix.xlsx
@@ -2705,7 +2705,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>Offen</t>
+          <t>Teilweise (Phase 4, Teil 2): Drucken über den Windows-Druckdialog mit Seitenauswahl, eingepasst</t>
         </is>
       </c>
     </row>
@@ -13382,7 +13382,7 @@
       <c r="N187" s="2" t="inlineStr"/>
       <c r="O187" s="2" t="inlineStr">
         <is>
-          <t>Offen</t>
+          <t>Umgesetzt (Phase 5, Teil 1): Ausschnitte per Rechtsklick auf eine Fläche</t>
         </is>
       </c>
     </row>

--- a/docs/phase1/EGLE360_PLAN_Funktionsmatrix.xlsx
+++ b/docs/phase1/EGLE360_PLAN_Funktionsmatrix.xlsx
@@ -13792,7 +13792,7 @@
       </c>
       <c r="O193" s="2" t="inlineStr">
         <is>
-          <t>Offen</t>
+          <t>Umgesetzt (Phase 5, Teil 1)</t>
         </is>
       </c>
     </row>

--- a/docs/phase1/EGLE360_PLAN_Funktionsmatrix.xlsx
+++ b/docs/phase1/EGLE360_PLAN_Funktionsmatrix.xlsx
@@ -12345,7 +12345,7 @@
       </c>
       <c r="O172" s="2" t="inlineStr">
         <is>
-          <t>Teilweise (Phase 5, Teil 1): CSV-Export für Excel; XLSX offen</t>
+          <t>Umgesetzt (Phase 5, Teil 2): XLSX mit Summenblatt, alternativ CSV</t>
         </is>
       </c>
     </row>
@@ -13177,7 +13177,7 @@
       <c r="N184" s="2" t="inlineStr"/>
       <c r="O184" s="2" t="inlineStr">
         <is>
-          <t>Offen</t>
+          <t>Umgesetzt (Phase 5, Teil 2): Tiefe je Fläche, Volumen in m³</t>
         </is>
       </c>
     </row>
@@ -13248,7 +13248,7 @@
       </c>
       <c r="O185" s="2" t="inlineStr">
         <is>
-          <t>Offen</t>
+          <t>Umgesetzt (Phase 5, Teil 2): Höhe je Länge, Polylänge oder Umfang, Wandfläche in m²</t>
         </is>
       </c>
     </row>
@@ -14726,7 +14726,7 @@
       <c r="N207" s="2" t="inlineStr"/>
       <c r="O207" s="2" t="inlineStr">
         <is>
-          <t>Teilweise (Phase 5, Teil 1): Mengenliste mit Summen und CSV-Export</t>
+          <t>Teilweise (Phase 5, Teil 2): Mengenliste mit Summen, Volumen und Wandflächen, Export als XLSX oder CSV</t>
         </is>
       </c>
     </row>

--- a/docs/phase1/EGLE360_PLAN_Funktionsmatrix.xlsx
+++ b/docs/phase1/EGLE360_PLAN_Funktionsmatrix.xlsx
@@ -8427,7 +8427,7 @@
       <c r="N114" s="2" t="inlineStr"/>
       <c r="O114" s="2" t="inlineStr">
         <is>
-          <t>Offen</t>
+          <t>Umgesetzt (Phase 5, Teil 2): Maßlinie mit Pfeilen, Zahl über der Linie, nach Seitenmaßstab</t>
         </is>
       </c>
     </row>
@@ -8833,7 +8833,7 @@
       </c>
       <c r="O120" s="2" t="inlineStr">
         <is>
-          <t>Offen</t>
+          <t>Teilweise (Phase 5, Teil 2): sieben eigene Textstempel und eigene Aufschrift, mit Autor und Datum; Bildstempel offen</t>
         </is>
       </c>
     </row>

--- a/docs/phase1/EGLE360_PLAN_Funktionsmatrix.xlsx
+++ b/docs/phase1/EGLE360_PLAN_Funktionsmatrix.xlsx
@@ -13654,7 +13654,7 @@
       <c r="N191" s="2" t="inlineStr"/>
       <c r="O191" s="2" t="inlineStr">
         <is>
-          <t>Offen</t>
+          <t>Umgesetzt (Phase 5, Teil 2): mit Kreisfläche in der Liste</t>
         </is>
       </c>
     </row>
@@ -13721,7 +13721,7 @@
       <c r="N192" s="2" t="inlineStr"/>
       <c r="O192" s="2" t="inlineStr">
         <is>
-          <t>Offen</t>
+          <t>Umgesetzt (Phase 5, Teil 2): mit Kreisfläche in der Liste</t>
         </is>
       </c>
     </row>

--- a/docs/phase1/EGLE360_PLAN_Funktionsmatrix.xlsx
+++ b/docs/phase1/EGLE360_PLAN_Funktionsmatrix.xlsx
@@ -8293,7 +8293,7 @@
       <c r="N112" s="2" t="inlineStr"/>
       <c r="O112" s="2" t="inlineStr">
         <is>
-          <t>Offen</t>
+          <t>Umgesetzt (Phase 5, Teil 2): Textfeld mit Pfeillinie, als FreeTextCallout gespeichert</t>
         </is>
       </c>
     </row>

--- a/docs/phase1/EGLE360_PLAN_Funktionsmatrix.xlsx
+++ b/docs/phase1/EGLE360_PLAN_Funktionsmatrix.xlsx
@@ -10713,7 +10713,7 @@
       <c r="N148" s="2" t="inlineStr"/>
       <c r="O148" s="2" t="inlineStr">
         <is>
-          <t>Offen</t>
+          <t>Umgesetzt (Phase 5, Teil 2): Sperren und Entsperren, im PDF zusätzlich mit Locked-Flag</t>
         </is>
       </c>
     </row>
@@ -12144,7 +12144,7 @@
       <c r="N169" s="2" t="inlineStr"/>
       <c r="O169" s="2" t="inlineStr">
         <is>
-          <t>Offen</t>
+          <t>Teilweise (Phase 5, Teil 2): sechs feste Status mit Person und Zeitpunkt; eigene Statusmodelle offen</t>
         </is>
       </c>
     </row>
@@ -14793,7 +14793,7 @@
       <c r="N208" s="2" t="inlineStr"/>
       <c r="O208" s="2" t="inlineStr">
         <is>
-          <t>Offen</t>
+          <t>Teilweise (Phase 5, Teil 2): Einheitspreis je Messung, Gesamtpreis und Kostensumme in Liste und Export; Preislisten je Werkzeug offen</t>
         </is>
       </c>
     </row>
@@ -14994,7 +14994,7 @@
       <c r="N211" s="2" t="inlineStr"/>
       <c r="O211" s="2" t="inlineStr">
         <is>
-          <t>Offen</t>
+          <t>Teilweise (Phase 5, Teil 2): Status Geprüft und Freigegeben mit Person und Zeitpunkt, Sperren; eigener Freigabeablauf offen</t>
         </is>
       </c>
     </row>

--- a/docs/phase1/EGLE360_PLAN_Funktionsmatrix.xlsx
+++ b/docs/phase1/EGLE360_PLAN_Funktionsmatrix.xlsx
@@ -8226,7 +8226,7 @@
       <c r="N111" s="2" t="inlineStr"/>
       <c r="O111" s="2" t="inlineStr">
         <is>
-          <t>Offen</t>
+          <t>Umgesetzt (Phase 5, Teil 2): als FreeTextTypeWriter gespeichert</t>
         </is>
       </c>
     </row>

--- a/docs/phase1/EGLE360_PLAN_Funktionsmatrix.xlsx
+++ b/docs/phase1/EGLE360_PLAN_Funktionsmatrix.xlsx
@@ -3620,7 +3620,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>Offen</t>
+          <t>Teilweise (Phase 5, Teil 2): vorherige und nächste Ansicht, Seite vor und zurück; erste und letzte Seite über das Seitenfeld</t>
         </is>
       </c>
     </row>

--- a/docs/phase1/EGLE360_PLAN_Funktionsmatrix.xlsx
+++ b/docs/phase1/EGLE360_PLAN_Funktionsmatrix.xlsx
@@ -10993,7 +10993,7 @@
       </c>
       <c r="O152" s="2" t="inlineStr">
         <is>
-          <t>Offen</t>
+          <t>Teilweise (Phase 5, Teil 2): Fang an End- und Mittelpunkten des Planinhalts und an Eckpunkten von Markierungen; Schnittpunkte und Raster offen</t>
         </is>
       </c>
     </row>

--- a/docs/phase1/EGLE360_PLAN_Funktionsmatrix.xlsx
+++ b/docs/phase1/EGLE360_PLAN_Funktionsmatrix.xlsx
@@ -10378,7 +10378,7 @@
       <c r="N143" s="2" t="inlineStr"/>
       <c r="O143" s="2" t="inlineStr">
         <is>
-          <t>Offen</t>
+          <t>Umgesetzt (Phase 5, Teil 2): sechs Ausrichtungen und Verteilen, bezogen auf die angezeigte Seitendrehung</t>
         </is>
       </c>
     </row>
@@ -10575,7 +10575,7 @@
       <c r="N146" s="2" t="inlineStr"/>
       <c r="O146" s="2" t="inlineStr">
         <is>
-          <t>Offen</t>
+          <t>Umgesetzt (Phase 5, Teil 2): Darstellung kopieren und einfügen (Strg+Umschalt+C/V)</t>
         </is>
       </c>
     </row>
@@ -12475,7 +12475,7 @@
       <c r="N174" s="2" t="inlineStr"/>
       <c r="O174" s="2" t="inlineStr">
         <is>
-          <t>Offen</t>
+          <t>Teilweise (Phase 5, Teil 2): alle Markierungen ein- und ausblenden; nach Art oder Autor offen</t>
         </is>
       </c>
     </row>

--- a/docs/phase1/EGLE360_PLAN_Funktionsmatrix.xlsx
+++ b/docs/phase1/EGLE360_PLAN_Funktionsmatrix.xlsx
@@ -8494,7 +8494,7 @@
       <c r="N115" s="2" t="inlineStr"/>
       <c r="O115" s="2" t="inlineStr">
         <is>
-          <t>Teilweise (Phase 4, Teil 2): Bereich hervorheben; an Textauswahl gebunden offen</t>
+          <t>Umgesetzt (Phase 4, Teil 3): folgt den Textzeilen im aufgezogenen Bereich, ohne Text als Rechteck</t>
         </is>
       </c>
     </row>
@@ -8561,7 +8561,7 @@
       <c r="N116" s="2" t="inlineStr"/>
       <c r="O116" s="2" t="inlineStr">
         <is>
-          <t>Offen</t>
+          <t>Umgesetzt (Phase 4, Teil 3): je Textzeile, als PDF-Underline mit QuadPoints</t>
         </is>
       </c>
     </row>
@@ -8628,7 +8628,7 @@
       <c r="N117" s="2" t="inlineStr"/>
       <c r="O117" s="2" t="inlineStr">
         <is>
-          <t>Offen</t>
+          <t>Umgesetzt (Phase 4, Teil 3): je Textzeile, als PDF-StrikeOut mit QuadPoints</t>
         </is>
       </c>
     </row>

--- a/docs/phase1/EGLE360_PLAN_Funktionsmatrix.xlsx
+++ b/docs/phase1/EGLE360_PLAN_Funktionsmatrix.xlsx
@@ -15061,7 +15061,7 @@
       <c r="N212" s="2" t="inlineStr"/>
       <c r="O212" s="2" t="inlineStr">
         <is>
-          <t>Offen</t>
+          <t>Umgesetzt (Phase 5, Teil 3): Werkzeugsätze in der Seitenleiste, Werkzeug aus Markierung speichern, bleibt beim Zeichnen aktiv</t>
         </is>
       </c>
     </row>
@@ -15195,7 +15195,7 @@
       </c>
       <c r="O214" s="2" t="inlineStr">
         <is>
-          <t>Offen</t>
+          <t>Teilweise (Phase 5, Teil 3): Import und Export im eigenen Format e360-tools (JSON); BTX-Import offen</t>
         </is>
       </c>
     </row>
@@ -15258,7 +15258,7 @@
       <c r="N215" s="2" t="inlineStr"/>
       <c r="O215" s="2" t="inlineStr">
         <is>
-          <t>Offen</t>
+          <t>Umgesetzt (Phase 5, Teil 3): Suche nach Name, Satz und Art; Favoriten zuerst</t>
         </is>
       </c>
     </row>
@@ -15329,7 +15329,7 @@
       </c>
       <c r="O216" s="2" t="inlineStr">
         <is>
-          <t>Offen</t>
+          <t>Teilweise (Phase 5, Teil 3): Grundausstattung Planprüfung und Mengen Hochbau ohne Preise; weitere Gewerke offen</t>
         </is>
       </c>
     </row>

--- a/docs/phase1/EGLE360_PLAN_Funktionsmatrix.xlsx
+++ b/docs/phase1/EGLE360_PLAN_Funktionsmatrix.xlsx
@@ -15459,7 +15459,7 @@
       <c r="N218" s="2" t="inlineStr"/>
       <c r="O218" s="2" t="inlineStr">
         <is>
-          <t>Offen</t>
+          <t>Umgesetzt (Phase 5, Teil 3): Planliste je Projektordner mit Nummer, Bezeichnung, Index, Datum, Verfasser, Gewerk, Geschoss, Gebäude, Bauabschnitt, Status, Freigabe; Excel-Export</t>
         </is>
       </c>
     </row>
@@ -15530,7 +15530,7 @@
       </c>
       <c r="O219" s="2" t="inlineStr">
         <is>
-          <t>Offen</t>
+          <t>Teilweise (Phase 5, Teil 3): Muster im Seitentext und im Dateinamen; Plankopf-Region und OCR offen</t>
         </is>
       </c>
     </row>
@@ -15601,7 +15601,7 @@
       </c>
       <c r="O220" s="2" t="inlineStr">
         <is>
-          <t>Offen</t>
+          <t>Teilweise (Phase 5, Teil 3): neue Indizes nach Plannummer einsortieren, mehrere Dateien auf einmal, Markierungen und Maßstäbe übernehmen</t>
         </is>
       </c>
     </row>
@@ -15664,7 +15664,7 @@
       <c r="N221" s="2" t="inlineStr"/>
       <c r="O221" s="2" t="inlineStr">
         <is>
-          <t>Offen</t>
+          <t>Umgesetzt (Phase 5, Teil 3): jeder Index bleibt als eigene Datei erhalten und lässt sich öffnen</t>
         </is>
       </c>
     </row>
@@ -15873,7 +15873,7 @@
       </c>
       <c r="O224" s="2" t="inlineStr">
         <is>
-          <t>Offen</t>
+          <t>Teilweise (Phase 5, Teil 3): Vorschlagsliste mit Gewerkkürzeln, frei änderbar</t>
         </is>
       </c>
     </row>

--- a/docs/phase1/EGLE360_PLAN_Funktionsmatrix.xlsx
+++ b/docs/phase1/EGLE360_PLAN_Funktionsmatrix.xlsx
@@ -10039,7 +10039,7 @@
       <c r="N138" s="2" t="inlineStr"/>
       <c r="O138" s="2" t="inlineStr">
         <is>
-          <t>Teilweise (Phase 4, Teil 2): Verschieben und Skalieren; Drehen offen</t>
+          <t>Umgesetzt (Phase 5, Teil 3): Verschieben, Skalieren, Drehen in 90-Grad-Schritten für alle Arten, beliebige Winkel für Punktformen</t>
         </is>
       </c>
     </row>
@@ -15940,7 +15940,7 @@
       </c>
       <c r="O225" s="2" t="inlineStr">
         <is>
-          <t>Offen</t>
+          <t>Teilweise (Phase 6, Teil 1): Seitenweiser Vergleich zweier Stände, Änderungen als Wolken im neuen Stand; stapelweise offen</t>
         </is>
       </c>
     </row>
@@ -16003,7 +16003,7 @@
       <c r="N226" s="2" t="inlineStr"/>
       <c r="O226" s="2" t="inlineStr">
         <is>
-          <t>Offen</t>
+          <t>Teilweise (Phase 6, Teil 1): Überlagerung rot (alt), blau (neu), grau (gleich); Ebenen und Transparenz offen</t>
         </is>
       </c>
     </row>

--- a/docs/phase1/EGLE360_PLAN_Funktionsmatrix.xlsx
+++ b/docs/phase1/EGLE360_PLAN_Funktionsmatrix.xlsx
@@ -16070,7 +16070,7 @@
       </c>
       <c r="O227" s="2" t="inlineStr">
         <is>
-          <t>Offen</t>
+          <t>Teilweise (Phase 6, Teil 1): Verschiebung wird automatisch erkannt und ausgeglichen; Drehung, Maßstab und manuelle Ausrichtung offen</t>
         </is>
       </c>
     </row>

--- a/docs/phase1/EGLE360_PLAN_Funktionsmatrix.xlsx
+++ b/docs/phase1/EGLE360_PLAN_Funktionsmatrix.xlsx
@@ -13315,7 +13315,7 @@
       </c>
       <c r="O186" s="2" t="inlineStr">
         <is>
-          <t>Offen</t>
+          <t>Umgesetzt (Phase 5): Neigung in Prozent bei Länge, Polylänge und Fläche; geneigte Länge oder Fläche und Höhenunterschied in Liste und Export. Ob die Rechenweise der Referenz entspricht, ist ungeprüft</t>
         </is>
       </c>
     </row>

--- a/docs/phase1/EGLE360_PLAN_Funktionsmatrix.xlsx
+++ b/docs/phase1/EGLE360_PLAN_Funktionsmatrix.xlsx
@@ -8967,7 +8967,7 @@
       <c r="N122" s="2" t="inlineStr"/>
       <c r="O122" s="2" t="inlineStr">
         <is>
-          <t>Offen</t>
+          <t>Umgesetzt (Phase 5): Bild aus Datei oder Zwischenablage, gezeichnetes Unterschriftsbild (keine digitale Signatur), speicherbar in der Werkzeugbibliothek; Scanner offen</t>
         </is>
       </c>
     </row>

--- a/docs/phase1/EGLE360_PLAN_Funktionsmatrix.xlsx
+++ b/docs/phase1/EGLE360_PLAN_Funktionsmatrix.xlsx
@@ -8900,7 +8900,7 @@
       <c r="N121" s="2" t="inlineStr"/>
       <c r="O121" s="2" t="inlineStr">
         <is>
-          <t>Offen</t>
+          <t>Umgesetzt (Phase 6): Stempel auf erste oder alle Seiten vieler Dateien, Ecke wählbar, als Kopien oder in den Originalen</t>
         </is>
       </c>
     </row>
@@ -17497,7 +17497,7 @@
       </c>
       <c r="O248" s="2" t="inlineStr">
         <is>
-          <t>Offen</t>
+          <t>Teilweise (Phase 6): Stapellauf mit Fortschritt, Protokoll, Abbruch und Fortsetzen über bereits erledigte Kopien; bisher Schritte Stempel und Maßstab</t>
         </is>
       </c>
     </row>

--- a/docs/phase1/EGLE360_PLAN_Funktionsmatrix.xlsx
+++ b/docs/phase1/EGLE360_PLAN_Funktionsmatrix.xlsx
@@ -16003,7 +16003,7 @@
       <c r="N226" s="2" t="inlineStr"/>
       <c r="O226" s="2" t="inlineStr">
         <is>
-          <t>Teilweise (Phase 6, Teil 1): Überlagerung rot (alt), blau (neu), grau (gleich); Ebenen und Transparenz offen</t>
+          <t>Teilweise (Phase 6): Überlagerung rot (alt), blau (neu), grau (gleich), jede Farbe ein- und ausblendbar; eigene Farben und Transparenz offen</t>
         </is>
       </c>
     </row>

--- a/docs/phase1/EGLE360_PLAN_Funktionsmatrix.xlsx
+++ b/docs/phase1/EGLE360_PLAN_Funktionsmatrix.xlsx
@@ -15802,7 +15802,7 @@
       <c r="N223" s="2" t="inlineStr"/>
       <c r="O223" s="2" t="inlineStr">
         <is>
-          <t>Offen</t>
+          <t>Teilweise (Phase 6): Änderungsbericht je Plan und Index aus dem Plansatzvergleich (Excel)</t>
         </is>
       </c>
     </row>
@@ -15940,7 +15940,7 @@
       </c>
       <c r="O225" s="2" t="inlineStr">
         <is>
-          <t>Teilweise (Phase 6, Teil 1): Seitenweiser Vergleich zweier Stände, Änderungen als Wolken im neuen Stand; stapelweise offen</t>
+          <t>Umgesetzt (Phase 6): Seitenweiser Vergleich zweier Stände, Änderungen als Wolken im neuen Stand, auch für ganze Plansätze</t>
         </is>
       </c>
     </row>
@@ -16070,7 +16070,7 @@
       </c>
       <c r="O227" s="2" t="inlineStr">
         <is>
-          <t>Teilweise (Phase 6, Teil 1): Verschiebung wird automatisch erkannt und ausgeglichen; Drehung, Maßstab und manuelle Ausrichtung offen</t>
+          <t>Offen</t>
         </is>
       </c>
     </row>
@@ -16141,7 +16141,7 @@
       </c>
       <c r="O228" s="2" t="inlineStr">
         <is>
-          <t>Offen</t>
+          <t>Teilweise (Phase 6): Verschiebung wird beim Vergleich automatisch erkannt und ausgeglichen; Drehung und Maßstab noch nicht</t>
         </is>
       </c>
     </row>
@@ -16212,7 +16212,7 @@
       </c>
       <c r="O229" s="2" t="inlineStr">
         <is>
-          <t>Offen</t>
+          <t>Teilweise (Phase 6): ganzer Plansatz der Planverwaltung, je Plan aktueller gegen vorherigen Index; freie Ordnervergleiche offen</t>
         </is>
       </c>
     </row>
@@ -16417,7 +16417,7 @@
       <c r="N232" s="2" t="inlineStr"/>
       <c r="O232" s="2" t="inlineStr">
         <is>
-          <t>Offen</t>
+          <t>Teilweise (Phase 6): Änderungsbericht als Excel-Mappe (je Plan und je Bereich), Wolken in die neuen Stände; PDF-Bericht und Aufgaben offen</t>
         </is>
       </c>
     </row>

--- a/docs/phase1/EGLE360_PLAN_Funktionsmatrix.xlsx
+++ b/docs/phase1/EGLE360_PLAN_Funktionsmatrix.xlsx
@@ -16070,7 +16070,7 @@
       </c>
       <c r="O227" s="2" t="inlineStr">
         <is>
-          <t>Offen</t>
+          <t>Umgesetzt (Phase 6): Passpunkte im alten und neuen Stand, ein Paar für Verschiebung, zwei Paare zusätzlich für Drehung und Maßstab</t>
         </is>
       </c>
     </row>

--- a/docs/phase1/EGLE360_PLAN_Funktionsmatrix.xlsx
+++ b/docs/phase1/EGLE360_PLAN_Funktionsmatrix.xlsx
@@ -2149,7 +2149,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>Offen</t>
+          <t>Teilweise (Phase 6): Kopf- und Fußzeile mit Dateiname, Seite, Seitenzahl und Datum über die Stapelverarbeitung, fest im Seiteninhalt; Entfernen und Bearbeiten offen</t>
         </is>
       </c>
     </row>
@@ -10851,7 +10851,7 @@
       <c r="N150" s="2" t="inlineStr"/>
       <c r="O150" s="2" t="inlineStr">
         <is>
-          <t>Offen</t>
+          <t>Teilweise (Phase 6): Einbrennen über die Stapelverarbeitung, Maßstab bleibt erhalten; Rückwandlung offen</t>
         </is>
       </c>
     </row>
@@ -17497,7 +17497,7 @@
       </c>
       <c r="O248" s="2" t="inlineStr">
         <is>
-          <t>Teilweise (Phase 6): Stapellauf mit Fortschritt, Protokoll, Abbruch und Fortsetzen über bereits erledigte Kopien; bisher Schritte Stempel und Maßstab</t>
+          <t>Teilweise (Phase 6): Stapellauf mit Fortschritt, Protokoll, Abbruch und Fortsetzen über bereits erledigte Kopien; Schritte Stempel, Maßstab, Kopf- und Fußzeile, Seiten drehen und Markierungen einbrennen</t>
         </is>
       </c>
     </row>
